--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DE7E48-C610-4070-96E8-5BEA9723F0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C80240A-86F0-4386-AE05-5EBB2EBBF575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2550" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="2895" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3922" uniqueCount="1409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4299" uniqueCount="1448">
   <si>
     <t>Name</t>
   </si>
@@ -4252,6 +4252,123 @@
   </si>
   <si>
     <t>BITTU TUKARI</t>
+  </si>
+  <si>
+    <t>SONU RAHUL</t>
+  </si>
+  <si>
+    <t>BALJEET VAKEEL</t>
+  </si>
+  <si>
+    <t>BALJEET VAKEEL HARMAN</t>
+  </si>
+  <si>
+    <t>0033</t>
+  </si>
+  <si>
+    <t>BALJEET VAKEEL HARDEV</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>BALJEET VAKEEL MANRAJ</t>
+  </si>
+  <si>
+    <t>BALJEET VAKEEL HUKUMAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALJEET VAKEEL </t>
+  </si>
+  <si>
+    <t>0820</t>
+  </si>
+  <si>
+    <t>BALJET VAKEEL</t>
+  </si>
+  <si>
+    <t>BALEET SUKHVINDER</t>
+  </si>
+  <si>
+    <t>BALJEET BALWANT</t>
+  </si>
+  <si>
+    <t>BALJEET BALJINDER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BALJEET AMAR </t>
+  </si>
+  <si>
+    <t>BALJEET BHJAN KAUR</t>
+  </si>
+  <si>
+    <t>SBIN002585</t>
+  </si>
+  <si>
+    <t>BALJET EDISAN</t>
+  </si>
+  <si>
+    <t>0158</t>
+  </si>
+  <si>
+    <t>BALJET GURVINDER SINGH</t>
+  </si>
+  <si>
+    <t>BALJET HARDEV</t>
+  </si>
+  <si>
+    <t>BALJEET FATHER SAAB</t>
+  </si>
+  <si>
+    <t>BAJEET VAKEL</t>
+  </si>
+  <si>
+    <t>BALEET VAKEEL</t>
+  </si>
+  <si>
+    <t>BALJEET HARDEV</t>
+  </si>
+  <si>
+    <t>UTIB0000507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUKHA KAITHULIYA </t>
+  </si>
+  <si>
+    <t>0092</t>
+  </si>
+  <si>
+    <t>0959</t>
+  </si>
+  <si>
+    <t>0967</t>
+  </si>
+  <si>
+    <t>0503</t>
+  </si>
+  <si>
+    <t>0180</t>
+  </si>
+  <si>
+    <t>0053</t>
+  </si>
+  <si>
+    <t>0802</t>
+  </si>
+  <si>
+    <t>9956</t>
+  </si>
+  <si>
+    <t>0620</t>
+  </si>
+  <si>
+    <t>0732</t>
+  </si>
+  <si>
+    <t>RR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RR</t>
   </si>
 </sst>
 </file>
@@ -4560,7 +4677,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C1372"/>
+  <dimension ref="A1:C1549"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -19659,6 +19776,1914 @@
         <v>2590</v>
       </c>
     </row>
+    <row r="1373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1373" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1373">
+        <v>4008</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1374" s="6" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1374" s="4" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1375" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1375" s="4" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1376" s="6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1376">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1377" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1377">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1378" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1378">
+        <v>3807</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1379" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1379" s="4" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1380" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1380">
+        <v>6173</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1381" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1381">
+        <v>9752</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1382" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1382">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1383" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1383">
+        <v>8675</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1384" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1384">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1385" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1385">
+        <v>9880</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1386" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1386" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1387" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1387">
+        <v>9613</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1388" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1388">
+        <v>8963</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1389" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1389" s="4" t="s">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1390" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C1390">
+        <v>9467</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1391" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1391">
+        <v>3829</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1392" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1392">
+        <v>9218</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1393" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1393">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1394" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1394">
+        <v>6398</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1395" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C1395">
+        <v>8853</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1396" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1396">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1397" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1397">
+        <v>4511</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1398" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1398">
+        <v>9197</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1399" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1399">
+        <v>3031</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1400" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1400">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1401" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1401" s="4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1402" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1402">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1403" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1403">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1404" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1404">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1405" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1405">
+        <v>4133</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1406" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1406">
+        <v>8836</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1407" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1407">
+        <v>6246</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1408" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1408">
+        <v>9775</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1409" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1409">
+        <v>9553</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1410" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1410">
+        <v>4784</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1411" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1411" s="4" t="s">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1412" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1412" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1413" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1413">
+        <v>6953</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1414" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1414">
+        <v>7106</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1415" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1415" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1416" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1416">
+        <v>3719</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1417" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1417">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1418" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1418">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1419" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1419">
+        <v>5857</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1420" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1420">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1421" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1421" s="4" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1422" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1422">
+        <v>9393</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1423" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1423">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1424" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1424">
+        <v>4915</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1425" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1425">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1426" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1426">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1427" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1427">
+        <v>6236</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1428" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1428">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1429" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1429">
+        <v>9455</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1430" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1430">
+        <v>3515</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1431" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1431">
+        <v>5239</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1432" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1432">
+        <v>4342</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1433" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1433">
+        <v>8030</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1434" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1434">
+        <v>6276</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1435" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1435">
+        <v>7707</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1436" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1436">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1437" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1437">
+        <v>5896</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1438" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1438">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1439" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1439">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1440" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1440">
+        <v>5291</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1441" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1441">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1442" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1442">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1443" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1443">
+        <v>5896</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1444" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1444" s="4" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1445" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1445">
+        <v>7923</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1446" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1446">
+        <v>6118</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1447" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1447">
+        <v>8287</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1448" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1448">
+        <v>2735</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1449" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1449">
+        <v>5033</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1450" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1450">
+        <v>8852</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1451" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1451">
+        <v>3641</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1452" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1452" s="4" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1453" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1453">
+        <v>4042</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1454" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1454">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1455" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1455">
+        <v>3226</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1456" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1456">
+        <v>3420</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1457" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1457">
+        <v>3423</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1458" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1458">
+        <v>3323</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1459" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1459">
+        <v>6074</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1460" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1460">
+        <v>8164</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1461" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1461">
+        <v>7754</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1462" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1462">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1463" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1463">
+        <v>9703</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1464" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1464">
+        <v>4775</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1465" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1465" s="4" t="s">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1466" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1466" s="4" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1467" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1467" s="4" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1468" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1468">
+        <v>3610</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1469" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1469">
+        <v>9580</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1470" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1470">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1471" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1471">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1472" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1472">
+        <v>6491</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1473" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1473" s="4" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1474" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1474">
+        <v>8280</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1475" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1475">
+        <v>5891</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1476" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1476">
+        <v>3701</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1477" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1477">
+        <v>5485</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1478" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1478">
+        <v>6301</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1479" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1479">
+        <v>4964</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1480" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1480" s="4" t="s">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1481" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1481">
+        <v>4054</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1482" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1482">
+        <v>3564</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1483" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1483">
+        <v>4052</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1484" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1484">
+        <v>1453</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1485" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1485">
+        <v>4948</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1486" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1486" s="4" t="s">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1487" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1487">
+        <v>5787</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1488" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1488">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1489" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1489">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1490" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1490">
+        <v>5917</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1491" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1491" s="4" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1492" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1492">
+        <v>6657</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1493" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1493">
+        <v>5494</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1494" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1494">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1495" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1495" s="4" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1496" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1496" s="4" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1497" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1497">
+        <v>5594</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1498" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1498" s="4" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1499" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1499">
+        <v>5135</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1500" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1500">
+        <v>7684</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1501" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1501">
+        <v>7077</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1502" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1502">
+        <v>6691</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1503" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1503" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1504" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1504">
+        <v>4256</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1505" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1505">
+        <v>7295</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1506" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1506">
+        <v>8092</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1507" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1507">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1508" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1508">
+        <v>9132</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1509" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1509">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1510" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1510">
+        <v>3993</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1511" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1511">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1512" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1512">
+        <v>7948</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1513" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1513">
+        <v>9790</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1514" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1514" s="4" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1515" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1515">
+        <v>4407</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1516" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1516">
+        <v>8471</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1517" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1517">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1518" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1518">
+        <v>9192</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1519" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1519">
+        <v>9628</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1520" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1520">
+        <v>6476</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1521" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1521">
+        <v>4705</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1522" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1522">
+        <v>6541</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1523" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1523">
+        <v>6403</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1524" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1524">
+        <v>8106</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1525" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1525">
+        <v>8619</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1526" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1526">
+        <v>5434</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1527" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1527">
+        <v>7377</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1528" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1528">
+        <v>9547</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1529" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1529">
+        <v>8480</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1530" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1530">
+        <v>9853</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1531" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1531">
+        <v>7542</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1532" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1532">
+        <v>5586</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1533" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1533">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1534" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1534">
+        <v>8562</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1535" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1535">
+        <v>7824</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1536" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1536">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1537" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1537">
+        <v>9785</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1538" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1539" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1540" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1541" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1542" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1543" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1544" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1545" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1546" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1547" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1548" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1549" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6996AAD-6DC3-4747-8F25-B67F8BD37645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201EFE7A-3AE2-4A79-A7D5-C9B2E3E69E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5110" uniqueCount="1498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5584" uniqueCount="1525">
   <si>
     <t>Name</t>
   </si>
@@ -4519,6 +4519,87 @@
   </si>
   <si>
     <t>IOBA0003256</t>
+  </si>
+  <si>
+    <t>KAUSLYA 22</t>
+  </si>
+  <si>
+    <t>MEENA KAUR TUKARI</t>
+  </si>
+  <si>
+    <t>RANA SATPAL</t>
+  </si>
+  <si>
+    <t>JASVEER kaur BHOD</t>
+  </si>
+  <si>
+    <t>DARSHAN GURMEET</t>
+  </si>
+  <si>
+    <t>LALA</t>
+  </si>
+  <si>
+    <t>;LALA</t>
+  </si>
+  <si>
+    <t>INDB0000022</t>
+  </si>
+  <si>
+    <t>INDB0000736</t>
+  </si>
+  <si>
+    <t>8134</t>
+  </si>
+  <si>
+    <t>INDUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHYAM </t>
+  </si>
+  <si>
+    <t>0636</t>
+  </si>
+  <si>
+    <t>BUA BARKIDADI</t>
+  </si>
+  <si>
+    <t>YESB0001099</t>
+  </si>
+  <si>
+    <t>0572</t>
+  </si>
+  <si>
+    <t>MOTTI</t>
+  </si>
+  <si>
+    <t>SURJEET BARNALA</t>
+  </si>
+  <si>
+    <t>GORU</t>
+  </si>
+  <si>
+    <t>2627</t>
+  </si>
+  <si>
+    <t>BICHAYI</t>
+  </si>
+  <si>
+    <t>LALI</t>
+  </si>
+  <si>
+    <t>BAPU ANKOHA</t>
+  </si>
+  <si>
+    <t>DIWAN CACHA</t>
+  </si>
+  <si>
+    <t>DARSAN</t>
+  </si>
+  <si>
+    <t>KANTU</t>
+  </si>
+  <si>
+    <t>0120</t>
   </si>
 </sst>
 </file>
@@ -11865,7 +11946,7 @@
     </row>
     <row r="640" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>680</v>
+        <v>1518</v>
       </c>
       <c r="B640" s="1" t="s">
         <v>46</v>
@@ -25858,192 +25939,420 @@
     </row>
     <row r="1912" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1912" t="s">
-        <v>1491</v>
+        <v>1498</v>
+      </c>
+      <c r="B1912" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1912" s="4">
+        <v>3827</v>
       </c>
     </row>
     <row r="1913" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1913" t="s">
-        <v>1491</v>
+        <v>1499</v>
+      </c>
+      <c r="B1913" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1913" s="4">
+        <v>4370</v>
       </c>
     </row>
     <row r="1914" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1914" t="s">
-        <v>1491</v>
+        <v>1500</v>
+      </c>
+      <c r="B1914" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1914" s="4">
+        <v>9385</v>
       </c>
     </row>
     <row r="1915" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1915" t="s">
-        <v>1491</v>
+        <v>1501</v>
+      </c>
+      <c r="B1915" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1915" s="4">
+        <v>6361</v>
       </c>
     </row>
     <row r="1916" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1916" t="s">
-        <v>1491</v>
+        <v>1502</v>
+      </c>
+      <c r="B1916" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1916" s="4">
+        <v>5666</v>
       </c>
     </row>
     <row r="1917" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1917" t="s">
-        <v>1491</v>
+        <v>1503</v>
+      </c>
+      <c r="B1917" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1917" s="4">
+        <v>7290</v>
       </c>
     </row>
     <row r="1918" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1918" t="s">
-        <v>1491</v>
+        <v>1503</v>
+      </c>
+      <c r="B1918" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1918" s="4">
+        <v>6095</v>
       </c>
     </row>
     <row r="1919" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1919" t="s">
-        <v>1491</v>
+        <v>1503</v>
+      </c>
+      <c r="B1919" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1919" s="4">
+        <v>7669</v>
       </c>
     </row>
     <row r="1920" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1920" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1921" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1503</v>
+      </c>
+      <c r="B1920" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1920" s="4">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1921" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1922" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1503</v>
+      </c>
+      <c r="B1921" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1921" s="4">
+        <v>6202</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1922" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1923" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1504</v>
+      </c>
+      <c r="B1922" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1922" s="4">
+        <v>6576</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1923" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1924" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1923" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C1923" s="4">
+        <v>4455</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1924" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1925" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1924" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1924" s="4">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1925" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1926" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1925" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1925" s="4">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1926" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1927" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1926" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1926" s="4">
+        <v>5678</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1927" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1928" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1927" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1927" s="4">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1928" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1929" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1928" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1928" s="4">
+        <v>5423</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1929" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1930" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1929" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1929" s="4">
+        <v>6775</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1930" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1931" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1930" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1930" s="4">
+        <v>8907</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1931" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1932" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1931" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1931" s="4">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1932" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1933" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1932" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1932" s="4">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1933" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1934" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1933" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1933" s="4">
+        <v>6754</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1934" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1935" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1934" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1934" s="4">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1935" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="1936" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1508</v>
+      </c>
+      <c r="B1935" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1935" s="4">
+        <v>3423</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1936" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1936" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1936" s="4">
+        <v>5643</v>
       </c>
     </row>
     <row r="1937" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1937" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1937" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1937" s="4">
+        <v>8767</v>
       </c>
     </row>
     <row r="1938" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1938" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1938" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1938" s="4">
+        <v>9865</v>
       </c>
     </row>
     <row r="1939" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1939" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1939" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1939" s="4">
+        <v>2345</v>
       </c>
     </row>
     <row r="1940" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1940" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1940" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1940" s="4">
+        <v>3423</v>
       </c>
     </row>
     <row r="1941" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1941" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1941" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1941" s="4">
+        <v>4532</v>
       </c>
     </row>
     <row r="1942" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1942" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1942" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1942" s="4">
+        <v>5432</v>
       </c>
     </row>
     <row r="1943" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1943" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1943" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1943" s="4">
+        <v>4532</v>
       </c>
     </row>
     <row r="1944" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1944" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1944" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1944" s="4">
+        <v>6547</v>
       </c>
     </row>
     <row r="1945" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1945" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1945" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1945" s="4">
+        <v>8745</v>
       </c>
     </row>
     <row r="1946" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1946" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1946" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1946" s="4">
+        <v>7354</v>
       </c>
     </row>
     <row r="1947" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1947" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1947" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1947" s="4">
+        <v>7243</v>
       </c>
     </row>
     <row r="1948" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1948" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1948" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1948" s="4">
+        <v>7613</v>
       </c>
     </row>
     <row r="1949" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1949" t="s">
-        <v>1491</v>
+        <v>1508</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1949" s="4">
+        <v>7254</v>
       </c>
     </row>
     <row r="1950" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -26068,10 +26377,2381 @@
         <v>1190</v>
       </c>
     </row>
+    <row r="1952" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1952" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1952" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1952" s="4">
+        <v>6598</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1953" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1953" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1953" s="4">
+        <v>9867</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1954" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1954" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1954" s="4">
+        <v>6754</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1955" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1955" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1955" s="4">
+        <v>7854</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1956" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1956" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1956" s="4">
+        <v>9812</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1957" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1957" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1957" s="4">
+        <v>5612</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1958" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1958" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1958" s="4">
+        <v>6123</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1959" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1959" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1959" s="4">
+        <v>6792</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1960" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1960" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1960" s="4">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1961" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1961" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1961" s="4">
+        <v>4123</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1962" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1962" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1962" s="4">
+        <v>8124</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1963" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1963" s="4">
+        <v>9190</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1964" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1964" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1964" s="4">
+        <v>8180</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1965" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1965" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1965" s="4">
+        <v>9145</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1966" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1966" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1966" s="4">
+        <v>7948</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1967" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1967" s="4">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1968" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1968" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1968" s="4">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1969" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1969" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1969" s="4">
+        <v>4034</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1970" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1970" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1970" s="4">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1971" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1971" s="4">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1972" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1972" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1972" s="4">
+        <v>3913</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1973" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1973" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1973" s="4">
+        <v>4891</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1974" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1974" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1974" s="4">
+        <v>5382</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1975" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1975" s="4">
+        <v>9146</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1976" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1976" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1976" s="4">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1977" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1977" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1977" s="4">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1978" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1978" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1978" s="4">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1979" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1979" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1979" s="4">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1980" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1980" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1980" s="4">
+        <v>7245</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1981" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1981" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1981" s="4">
+        <v>7234</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1982" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1982" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1982" s="4">
+        <v>7512</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1983" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1983" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1983" s="4">
+        <v>7245</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1984" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1984" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1984" s="4">
+        <v>8754</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1985" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1985" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1985" s="4">
+        <v>8934</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1986" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1986" s="4">
+        <v>9123</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1987" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1987" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1987" s="4" t="s">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1988" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1988" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1988" s="4">
+        <v>6532</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1989" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1989" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1989" s="4">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1990" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1990" s="4">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1991" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1991" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1991" s="4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1992" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1992" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1992" s="4">
+        <v>9765</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1993" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1993" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1993" s="4">
+        <v>4743</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1994" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1994" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1994" s="4">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1995" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1995" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1995" s="4">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1996" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1996" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1996" s="4">
+        <v>6789</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1997" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1997" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1997" s="4">
+        <v>5678</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1998" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1998" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1998" s="4">
+        <v>9876</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1999" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1999" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C1999" s="4">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2000" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B2000" t="s">
+        <v>1506</v>
+      </c>
+      <c r="C2000" s="4">
+        <v>7654</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2001" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B2001" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2001" s="4">
+        <v>8267</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2002" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2002" s="4">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2003" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B2003" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C2003" s="4">
+        <v>8552</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2004" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B2004" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2004" s="4" t="s">
+        <v>1510</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2005" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2005" s="4">
+        <v>7524</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2006" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2006" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2006" s="4">
+        <v>5563</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2007" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2007" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2007" s="4">
+        <v>3481</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2008" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2008" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2008" s="4">
+        <v>4354</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2009" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2009" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2009" s="4">
+        <v>4672</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2010" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2010" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2010" s="4">
+        <v>5806</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2011" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2011" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2011" s="4">
+        <v>8073</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2012" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2012" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2012" s="4">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2013" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2013" t="s">
+        <v>1512</v>
+      </c>
+      <c r="C2013" s="4">
+        <v>5571</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2014" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2014" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2014" s="4">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2015" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B2015" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2015" s="4" t="s">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2016" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B2016" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2016" s="4">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2017" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B2017" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2017" s="4">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2018" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2018" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2018" s="4">
+        <v>5756</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2019" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2019" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2019" s="4">
+        <v>5677</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2020" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2020" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2020" s="4">
+        <v>5695</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2021" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2021" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2021" s="4">
+        <v>5744</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2022" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2022" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2022" s="4">
+        <v>7989</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2023" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2023" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2023" s="4">
+        <v>8871</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2024" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2024" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2024" s="4">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2025" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2025" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2025" s="4">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2026" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2026" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2026" s="4">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2027" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2027" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2027" s="4">
+        <v>9710</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2028" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2028" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2028" s="4">
+        <v>3367</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2029" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2029" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2029" s="4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2030" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2030" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2030" s="4">
+        <v>3878</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2031" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2031" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2031" s="4">
+        <v>6953</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2032" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2032" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2032" s="4">
+        <v>2933</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2033" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2033" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2033" s="4">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2034" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2034" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2034" s="4">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2035" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2035" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2035" s="4" t="s">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2036" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2036" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2036" s="4">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2037" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2037" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2037" s="4">
+        <v>8619</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2038" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2038" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2038" s="4">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2039" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2039" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2039" s="4">
+        <v>4407</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2040" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2040" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2040" s="4">
+        <v>8471</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2041" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2041" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2041" s="4">
+        <v>9192</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2042" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2042" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2042" s="4">
+        <v>9628</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2043" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2043" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2043" s="4">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2044" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2044" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2044" s="4">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2045" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2045" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2045" s="4">
+        <v>4874</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2046" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2046" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2046" s="4">
+        <v>6541</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2047" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2047" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2047" s="4">
+        <v>6403</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2048" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2048" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2048" s="4">
+        <v>7469</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2049" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2049" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2049" s="4">
+        <v>3658</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2050" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2050" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2050" s="4">
+        <v>3631</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2051" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2051" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2051" s="4">
+        <v>9729</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2052" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2052" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2052" s="4">
+        <v>6108</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2053" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2053" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2053" s="4">
+        <v>8178</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2054" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2054" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2054" s="4">
+        <v>7895</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2055" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2055" s="4">
+        <v>4439</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2056" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2056" s="4">
+        <v>3312</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2057" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2057" s="4">
+        <v>9785</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2058" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2058" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2058" s="4">
+        <v>7096</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2059" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2059" s="4">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2060" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2060" s="4">
+        <v>7824</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2061" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2061" s="4">
+        <v>8561</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2062" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2062" s="4">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2063" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2063" s="4">
+        <v>5586</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2064" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2064" s="4">
+        <v>7542</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2065" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2065" s="4">
+        <v>9853</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2066" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2066" s="4">
+        <v>8480</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2067" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2067" s="4">
+        <v>9547</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2068" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2068" s="4">
+        <v>7377</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2069" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2069" s="4">
+        <v>5434</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2070" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2070" s="4">
+        <v>9262</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2071" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2071" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2071" s="4">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2072" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2072" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2072" s="4">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2073" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2073" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2073" s="4">
+        <v>9267</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2074" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2074" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2074" s="4">
+        <v>5660</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2075" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2075" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2075" s="4">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2076" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2076" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2076" s="4">
+        <v>4106</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2077" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2077" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2077" s="4">
+        <v>4957</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2078" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2078" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2078" s="4">
+        <v>5699</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2079" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2079" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2079" s="4">
+        <v>8287</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2080" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2080" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2080" s="4" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2081" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2081" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2081" s="4">
+        <v>6912</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2082" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2082" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2082" s="4">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2083" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2083" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2083" s="4">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2084" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2084" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2084" s="4">
+        <v>6129</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2085" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2085" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2085" s="4">
+        <v>6569</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2086" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2086" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2086" s="4">
+        <v>9831</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2087" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2087" s="4">
+        <v>3943</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2088" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2088" s="4">
+        <v>7911</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2089" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2089" s="4">
+        <v>3731</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2090" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2090" s="4">
+        <v>6067</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2091" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2091" s="4">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2092" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2092" s="4">
+        <v>6349</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2093" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2093" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2093" s="4">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2094" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2094" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2094" s="4">
+        <v>8438</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2095" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2095" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2095" s="4">
+        <v>5797</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2096" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2096" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2096" s="4">
+        <v>5775</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2097" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2097" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2097" s="4">
+        <v>9218</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2098" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2098" s="4">
+        <v>3911</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2099" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2099" s="4">
+        <v>8686</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2100" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2100" s="4">
+        <v>4579</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2101" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2101" s="4">
+        <v>4635</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2102" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2102" s="4">
+        <v>5930</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2103" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2103" s="4">
+        <v>6159</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2104" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2104" s="4">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2105" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2105" s="4">
+        <v>6371</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2106" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2106" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2106" s="4">
+        <v>3628</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2107" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2107" s="4">
+        <v>9240</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2108" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2108" s="4">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2109" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2109" s="4">
+        <v>5455</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2110" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2110" s="4">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2111" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2111" s="4">
+        <v>8931</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2112" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2112" s="4">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2113" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2113" s="4">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2114" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2114" s="4">
+        <v>9150</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2115" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2115" s="4">
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2116" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2116" s="4">
+        <v>6912</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2117" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2117" s="4">
+        <v>3530</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2118" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2118" s="4">
+        <v>9267</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2119" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2119" s="4">
+        <v>9262</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2120" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2120" s="4">
+        <v>9062</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2121" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2121" s="4">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2122" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2122" s="4">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2123" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2123" s="4">
+        <v>9853</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2124" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2124" s="4">
+        <v>8480</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2125" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2125" s="4">
+        <v>9547</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2126" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2126" s="4">
+        <v>7377</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2127" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2127" s="4">
+        <v>5434</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2128" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2128" s="4">
+        <v>4553</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2129" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2129" s="4">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2130" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2130" s="4">
+        <v>9262</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2131" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2131" s="4">
+        <v>8972</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2132" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2132" s="4">
+        <v>2751</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2133" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2133" s="4">
+        <v>3207</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2134" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2134" s="4">
+        <v>7824</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2135" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2135" s="4">
+        <v>8561</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2136" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2136" s="4">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2137" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2137" s="4">
+        <v>5586</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2138" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2138" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2138" s="4">
+        <v>7542</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2139" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2139" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2139" s="4">
+        <v>9267</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2140" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2140" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2140" s="4">
+        <v>3744</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2141" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2141" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2141" s="4">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2142" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2142" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2142" s="4">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2143" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2143" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2143" s="4">
+        <v>6336</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2144" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2144" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2144" s="4">
+        <v>8123</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2145" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2145" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2145" s="4">
+        <v>7706</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2146" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2146" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2146" s="4">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2147" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B2147" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2147" s="4">
+        <v>9267</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2148" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B2148" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2148" s="4">
+        <v>7290</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2149" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B2149" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2149" s="4">
+        <v>6095</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2150" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B2150" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2150" s="4">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2151" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B2151" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2151" s="4">
+        <v>7669</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2152" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B2152" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2152" s="4">
+        <v>3579</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2153" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B2153" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2153" s="4">
+        <v>4434</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2154" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B2154" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2154" s="4">
+        <v>6585</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2155" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B2155" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2155" s="4">
+        <v>8183</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2156" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B2156" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2156" s="4">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2157" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2157" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2157" s="4">
+        <v>9217</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2158" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2158" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2158" s="4">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2159" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2159" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2159" s="4">
+        <v>1787</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2160" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2160" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2160" s="4">
+        <v>3115</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2161" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2161" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2161" s="4">
+        <v>3591</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2162" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2162" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2162" s="4" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2163" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2163" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2163" s="4">
+        <v>7752</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2164" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2164" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2164" s="4">
+        <v>5132</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2165" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2165" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2165" s="4">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2166" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B2166" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2166" s="4">
+        <v>5271</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2167" s="4"/>
+    </row>
+    <row r="2168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2168" s="4"/>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">
-        <v>1491</v>
+        <v>1516</v>
       </c>
       <c r="B1048576" t="s">
         <v>46</v>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39012805-304C-4DDD-95CA-AB9FA1967DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744BE2CE-9DC4-43E0-ABF3-3A89672FF903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5529" uniqueCount="1427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5537" uniqueCount="1430">
   <si>
     <t>Name</t>
   </si>
@@ -4306,6 +4306,15 @@
   </si>
   <si>
     <t>0308</t>
+  </si>
+  <si>
+    <t>MAMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LALA WIFE </t>
+  </si>
+  <si>
+    <t>KANTU NEW</t>
   </si>
 </sst>
 </file>
@@ -28931,6 +28940,50 @@
         <v>8785</v>
       </c>
     </row>
+    <row r="2211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2211" s="6" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B2211" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2211">
+        <v>2705</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2212" s="6" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B2212" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2212">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2213" s="6" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B2213" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2213">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2214" s="6" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B2214" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2214">
+        <v>9072</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744BE2CE-9DC4-43E0-ABF3-3A89672FF903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF66C152-2304-44C1-B323-58F0F82AF2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5537" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5594" uniqueCount="1444">
   <si>
     <t>Name</t>
   </si>
@@ -4315,6 +4315,48 @@
   </si>
   <si>
     <t>KANTU NEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALKEET RINKU </t>
+  </si>
+  <si>
+    <t>MALKEET RINKU MINDER</t>
+  </si>
+  <si>
+    <t>MALKEET RINKU RAJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALKEET MALKEET </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALKEET BHJAN </t>
+  </si>
+  <si>
+    <t>MALKEET MINDER</t>
+  </si>
+  <si>
+    <t>MALKEET SARVJEET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MALKEET MANRAJJ </t>
+  </si>
+  <si>
+    <t>JITEDER MALKEET RINKU</t>
+  </si>
+  <si>
+    <t>MALKEET PAPA</t>
+  </si>
+  <si>
+    <t>MALKEET KOSYLYA RINKU</t>
+  </si>
+  <si>
+    <t>MALKEET RAJ</t>
+  </si>
+  <si>
+    <t>0211</t>
+  </si>
+  <si>
+    <t>SBINORRUTGB</t>
   </si>
 </sst>
 </file>
@@ -28984,6 +29026,292 @@
         <v>9072</v>
       </c>
     </row>
+    <row r="2215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2215" s="6" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B2215" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2215">
+        <v>6545</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2216" s="6" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B2216" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2216">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2217" s="6" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B2217" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2217">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2218" s="6" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B2218" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2218">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2219" s="6" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B2219" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2219">
+        <v>5549</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2220" s="6" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B2220" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2220">
+        <v>7827</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2221" s="6" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B2221" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2221" s="4" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2222" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B2222" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2222">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2223" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B2223" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2223">
+        <v>3874</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2224" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B2224" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2224">
+        <v>7167</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2225" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B2225" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2225">
+        <v>3625</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2226" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B2226" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2226" s="4" t="s">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2227" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2227" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2227">
+        <v>5664</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2228" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B2228" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2228">
+        <v>5642</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2229" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B2229" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2229">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2230" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2230" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2230" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2231" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2231" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2231">
+        <v>4065</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2232" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2232" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2232">
+        <v>3497</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2233" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2233" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2233">
+        <v>6830</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2234" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2234" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2234">
+        <v>6341</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2235" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2235" t="s">
+        <v>1443</v>
+      </c>
+      <c r="C2235">
+        <v>4314</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2236" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2236" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2236" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2237" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2237" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C2237">
+        <v>9322</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2238" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2238" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2238">
+        <v>9855</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2239" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2239" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2239" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2240" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B2240" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2240">
+        <v>6429</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF66C152-2304-44C1-B323-58F0F82AF2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D98CBC8-6884-40D2-A1F8-0DE1877FAF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5594" uniqueCount="1444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5667" uniqueCount="1445">
   <si>
     <t>Name</t>
   </si>
@@ -4357,13 +4357,16 @@
   </si>
   <si>
     <t>SBINORRUTGB</t>
+  </si>
+  <si>
+    <t>0167</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4416,6 +4419,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1B1B1D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4437,7 +4447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4452,6 +4462,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -29239,7 +29250,7 @@
       <c r="A2234" t="s">
         <v>1238</v>
       </c>
-      <c r="B2234" t="s">
+      <c r="B2234" s="6" t="s">
         <v>58</v>
       </c>
       <c r="C2234">
@@ -29310,6 +29321,402 @@
       </c>
       <c r="C2240">
         <v>6429</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2241" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2241" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2241">
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2242" s="12" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2242" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2242">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2243" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2243" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2243">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2244" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2244" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2244">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2245" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2245" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2245">
+        <v>3341</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2246" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2246" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2246">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2247" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2247" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2247">
+        <v>6205</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2248" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2248" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2248">
+        <v>7720</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2249" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2249" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2249">
+        <v>6674</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2250" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2250" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2250">
+        <v>5381</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2251" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2251" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2251">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2252" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2252" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2252">
+        <v>6691</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2253" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2253" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2253">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2254" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2254" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2254">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2255" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2255" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2255">
+        <v>5801</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2256" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2256" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2256">
+        <v>5773</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2257" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2257" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2257">
+        <v>7702</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2258" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2258" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2258">
+        <v>5219</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2259" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2259" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2259">
+        <v>8191</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2260" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2260" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2260">
+        <v>8984</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2261" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2261" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2261">
+        <v>5226</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2262" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2262" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2262">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2263" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2263" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2263">
+        <v>3141</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2264" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2264" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2264">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2265" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2265" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2265">
+        <v>5804</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2266" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2266" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2266">
+        <v>8852</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2267" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2267" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2267">
+        <v>9334</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2268" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2268" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2268">
+        <v>5833</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2269" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2269" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2269">
+        <v>9855</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2270" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2270" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2270">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2271" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2271" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2271">
+        <v>6530</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2272" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2272" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2272" s="5" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2273" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2273" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2273">
+        <v>7128</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2274" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2274" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2274">
+        <v>3839</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2275" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2275" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2275">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2276" s="6" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B2276" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2276">
+        <v>5957</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8537A2F-A7BC-4EF4-99C7-C50126CB8C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340CEF12-3320-4C3A-A586-B4A875B37BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5497" uniqueCount="1306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5756" uniqueCount="1317">
   <si>
     <t>Name</t>
   </si>
@@ -3943,6 +3943,39 @@
   </si>
   <si>
     <t>0062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLDI PAMMU </t>
+  </si>
+  <si>
+    <t>0597</t>
+  </si>
+  <si>
+    <t>PRINCE</t>
+  </si>
+  <si>
+    <t>0807</t>
+  </si>
+  <si>
+    <t>0303</t>
+  </si>
+  <si>
+    <t>0418</t>
+  </si>
+  <si>
+    <t>0556</t>
+  </si>
+  <si>
+    <t>0883</t>
+  </si>
+  <si>
+    <t>0659</t>
+  </si>
+  <si>
+    <t>0648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARSN PNB </t>
   </si>
 </sst>
 </file>
@@ -11635,7 +11668,7 @@
         <v>557</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>558</v>
@@ -18972,7 +19005,7 @@
         <v>1089</v>
       </c>
       <c r="B1337" s="9" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C1337">
         <v>2488</v>
@@ -29350,6 +29383,1381 @@
       </c>
       <c r="C2280">
         <v>3942</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2281" s="6" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B2281" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2281">
+        <v>7641</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2282" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B2282" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2282">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2283" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2283" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2283">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2284" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2284" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2284">
+        <v>9144</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2285" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2285" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2285">
+        <v>4097</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2286" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B2286" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2286">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2287" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2287" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2287" s="4" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2288" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2288" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2288">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2289" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2289" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2289">
+        <v>9455</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2290" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2290" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2290">
+        <v>6866</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2291" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2291" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2291">
+        <v>3138</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2292" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2292" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2292">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2293" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2293" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2293">
+        <v>6544</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2294" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2294" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2294">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2295" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2295" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2295">
+        <v>4840</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2296" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2296" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2296">
+        <v>5163</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2297" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2297" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2297">
+        <v>6995</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2298" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2298" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2298">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2299" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B2299" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2299">
+        <v>9476</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2300" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2300" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2300">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2301" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2301" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2301">
+        <v>8220</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2302" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2302" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2302">
+        <v>5022</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2303" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2303" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2303">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2304" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2304" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2304">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2305" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2305" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2305">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2306" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2306" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2306">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2307" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2307" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2307">
+        <v>4084</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2308" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2308" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2308">
+        <v>8505</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2309" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2309" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2309">
+        <v>3164</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2310" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2310" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2310" s="4" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2311" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2311" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2311">
+        <v>5974</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2312" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2312" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2312">
+        <v>5967</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2313" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2313" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2313">
+        <v>6409</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2314" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2314" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2314">
+        <v>8100</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2315" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2315" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2315">
+        <v>8659</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2316" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2316" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2316">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2317" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2317" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2317">
+        <v>7034</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2318" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2318" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2318">
+        <v>5081</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2319" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2319" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2319">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2320" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2320" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2320">
+        <v>8652</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2321" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2321" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2321" s="4" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2322" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2322" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2322">
+        <v>8025</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2323" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2323" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2323">
+        <v>3620</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2324" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2324" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2324">
+        <v>3668</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2325" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2325" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2325">
+        <v>8641</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2326" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2326" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2326">
+        <v>5298</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2327" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2327" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2327">
+        <v>7295</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2328" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2328" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2328">
+        <v>5987</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2329" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2329" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2329">
+        <v>7391</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2330" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2330" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2330">
+        <v>7027</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2331" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2331" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2331" s="4" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2332" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2332" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2332">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2333" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2333" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2333">
+        <v>8974</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2334" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2334" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2334">
+        <v>8117</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2335" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2335" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2335">
+        <v>8518</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2336" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2336" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2336">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2337" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2337" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2337">
+        <v>7211</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2338" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2338" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2338">
+        <v>9846</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2339" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2339" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2339">
+        <v>7947</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2340" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2340" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2340">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2341" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2341" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2341">
+        <v>5249</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2342" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2342" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2342">
+        <v>8319</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2343" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2343" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2343">
+        <v>8990</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2344" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2344" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2344">
+        <v>5892</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2345" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2345" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2345">
+        <v>5750</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2346" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2346" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2346">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2347" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2347" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2347">
+        <v>5720</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2348" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2348" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2348">
+        <v>2760</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2349" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2349" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2349">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2350" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2350" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2350" s="4" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2351" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2351" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2351">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2352" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2352" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2352">
+        <v>7979</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2353" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2353" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2353">
+        <v>9308</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2354" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2354" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2354">
+        <v>6525</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2355" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2355" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2355">
+        <v>3557</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2356" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2356" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2356">
+        <v>8814</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2357" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2357" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2357">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2358" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2358" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2358">
+        <v>5696</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2359" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2359" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2359">
+        <v>7677</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2360" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2360" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2360">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2361" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2361" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2361">
+        <v>9137</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2362" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2362" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2362">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2363" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2363" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2363">
+        <v>9858</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2364" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2364" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2364">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2365" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2365" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2365">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2366" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2366" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2366">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2367" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2367" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2367">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2368" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2368" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2368">
+        <v>2984</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2369" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2369" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2369">
+        <v>7011</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2370" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2370" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2370">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2371" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2371" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2371">
+        <v>4158</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2372" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2372" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2372">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2373" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2373" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2373">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2374" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2374" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2374">
+        <v>3152</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2375" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2375" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2375">
+        <v>9761</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2376" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2376" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2376">
+        <v>4010</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2377" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2377" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2377">
+        <v>8261</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2378" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2378" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2378">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2379" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2379" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2379">
+        <v>4795</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2380" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2380" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2380">
+        <v>4403</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2381" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2381" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2381">
+        <v>5977</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2382" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2382" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2382">
+        <v>4683</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2383" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2383" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2383">
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2384" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2384" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2384">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2385" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2385" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2385">
+        <v>8691</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2386" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2386" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2386">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2387" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2387" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2387" s="4" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2388" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2388" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2388">
+        <v>6962</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2389" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2389" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2389">
+        <v>1474</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2390" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2390" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2390">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2391" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2391" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2391">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2392" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2392" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2392" s="4" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2393" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2393" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2393" s="4" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2394" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2394" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2394">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2395" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2395" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2395">
+        <v>5277</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2396" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2396" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2396">
+        <v>7918</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2397" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2397" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2397">
+        <v>3770</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2398" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2398" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2398">
+        <v>8866</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2399" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2399" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2399">
+        <v>9850</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2400" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2400" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2400">
+        <v>4894</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2401" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2401" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2401">
+        <v>5055</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2402" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2402" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2402" s="4" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2403" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2403" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2403">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2404" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B2404" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2404">
+        <v>7846</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2405" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B2405" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2405">
+        <v>7836</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340CEF12-3320-4C3A-A586-B4A875B37BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D9137D-E0A5-46C6-BDE1-B7BF078C1899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5756" uniqueCount="1317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5800" uniqueCount="1319">
   <si>
     <t>Name</t>
   </si>
@@ -3976,6 +3976,12 @@
   </si>
   <si>
     <t xml:space="preserve">DARSN PNB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GURMEL PNB </t>
+  </si>
+  <si>
+    <t>SUKHU</t>
   </si>
 </sst>
 </file>
@@ -25608,9 +25614,7 @@
       <c r="B1937" t="s">
         <v>1214</v>
       </c>
-      <c r="C1937" s="4">
-        <v>8767</v>
-      </c>
+      <c r="C1937" s="4"/>
     </row>
     <row r="1938" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1938" t="s">
@@ -30758,6 +30762,248 @@
       </c>
       <c r="C2405">
         <v>7836</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2406" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B2406" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2406">
+        <v>7246</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2407" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B2407" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2407">
+        <v>9932</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2408" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B2408" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2408">
+        <v>7365</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2409" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B2409" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2409">
+        <v>8329</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2410" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B2410" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2410">
+        <v>5893</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2411" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B2411" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2411">
+        <v>8368</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2412" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B2412" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2412">
+        <v>5388</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2413" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B2413" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2413">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2414" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B2414" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2414">
+        <v>3565</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2415" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B2415" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2415">
+        <v>1466</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2416" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2416" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2416">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2417" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2417" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2417">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2418" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2418" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2418">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2419" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2419" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2419">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2420" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2420" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2420">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2421" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2421" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2421">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2422" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2422" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2422">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2423" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2423" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2423">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2424" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2424" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2424">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2425" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2425" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2425">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2426" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2426" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2426">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2428" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B2428" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2428">
+        <v>1444</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7CB1358-C73F-4ABA-933D-DD2AEF0B32EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDBE265-96B3-4685-AAB4-B3EDE193966E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5850" uniqueCount="1331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5884" uniqueCount="1337">
   <si>
     <t>Name</t>
   </si>
@@ -4018,6 +4018,24 @@
   </si>
   <si>
     <t>BITTU BAGIYA</t>
+  </si>
+  <si>
+    <t>PAMU GOLDI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARAN PNB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUKHDEV </t>
+  </si>
+  <si>
+    <t>GOPI</t>
+  </si>
+  <si>
+    <t>UBIN0557978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JASVANT BAGIYA </t>
   </si>
 </sst>
 </file>
@@ -31311,6 +31329,193 @@
         <v>6183</v>
       </c>
     </row>
+    <row r="2454" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2454" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B2454" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2454">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2455" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B2455" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2455">
+        <v>3742</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2456" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B2456" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2456">
+        <v>9101</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2457" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B2457" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2457">
+        <v>7598</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2458" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B2458" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2458">
+        <v>4156</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2459" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B2459" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2459">
+        <v>3663</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2460" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B2460" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2460">
+        <v>9165</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2461" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B2461" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2461">
+        <v>8712</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2462" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B2462" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2462">
+        <v>6822</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2463" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B2463" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C2463">
+        <v>7071</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2464" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B2464" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2464">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2465" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2465" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2465">
+        <v>9160</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2466" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2466" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2466">
+        <v>5139</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2467" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2467" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2467">
+        <v>8149</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2468" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2468" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2468">
+        <v>9405</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2469" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2469" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2469">
+        <v>5817</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2470" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2470" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2470">
+        <v>9056</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDBE265-96B3-4685-AAB4-B3EDE193966E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01D0356-386C-443D-8B96-6C4D1E8D26B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5884" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5910" uniqueCount="1339">
   <si>
     <t>Name</t>
   </si>
@@ -4036,6 +4036,12 @@
   </si>
   <si>
     <t xml:space="preserve">JASVANT BAGIYA </t>
+  </si>
+  <si>
+    <t>0752</t>
+  </si>
+  <si>
+    <t>0498</t>
   </si>
 </sst>
 </file>
@@ -31516,6 +31522,138 @@
         <v>9056</v>
       </c>
     </row>
+    <row r="2471" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2471" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2471" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2471">
+        <v>4665</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2472" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2472" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2472" s="4" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2473" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2473" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2473">
+        <v>7418</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2474" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2474" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2474">
+        <v>7046</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2475" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2475" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2475">
+        <v>3847</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2476" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2476" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2476">
+        <v>7246</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2477" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2477" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2477">
+        <v>5893</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2478" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2478" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2478">
+        <v>8329</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2479" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2479" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2479">
+        <v>7365</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2480" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2480" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2480">
+        <v>9932</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2481" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2481" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2481" s="4" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2482" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2482" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2482">
+        <v>1218</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C01D0356-386C-443D-8B96-6C4D1E8D26B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11B9AA7-412D-4870-9D6F-DF600EE436D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5910" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5923" uniqueCount="1340">
   <si>
     <t>Name</t>
   </si>
@@ -4042,6 +4042,9 @@
   </si>
   <si>
     <t>0498</t>
+  </si>
+  <si>
+    <t>0428</t>
   </si>
 </sst>
 </file>
@@ -31654,6 +31657,72 @@
         <v>1218</v>
       </c>
     </row>
+    <row r="2483" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2483" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B2483" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2483" s="4" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2484" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B2484" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2484">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2485" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B2485" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2485" s="4">
+        <v>8575</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2486" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B2486" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2486">
+        <v>9815</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2487" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B2487" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2487" s="4">
+        <v>5431</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2488" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B2488" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2488">
+        <v>6093</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11B9AA7-412D-4870-9D6F-DF600EE436D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C8AE80-0C0D-4343-BF98-64F518D55BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5923" uniqueCount="1340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5937" uniqueCount="1341">
   <si>
     <t>Name</t>
   </si>
@@ -4045,6 +4045,9 @@
   </si>
   <si>
     <t>0428</t>
+  </si>
+  <si>
+    <t>SHITU</t>
   </si>
 </sst>
 </file>
@@ -17927,7 +17930,7 @@
         <v>35</v>
       </c>
       <c r="C1233">
-        <v>9591</v>
+        <v>9551</v>
       </c>
     </row>
     <row r="1234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22195,7 +22198,7 @@
         <v>35</v>
       </c>
       <c r="C1621">
-        <v>1726</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1622" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -31323,9 +31326,6 @@
       <c r="B2452" t="s">
         <v>44</v>
       </c>
-      <c r="C2452">
-        <v>4570</v>
-      </c>
     </row>
     <row r="2453" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2453" t="s">
@@ -31721,6 +31721,83 @@
       </c>
       <c r="C2488">
         <v>6093</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2489" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B2489" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2489" s="4">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2490" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2490" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2490">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2491" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2491" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2491" s="4">
+        <v>4086</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2492" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2492" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2492">
+        <v>5294</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2493" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2493" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2493" s="4">
+        <v>3842</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2494" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2494" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2494">
+        <v>9583</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2495" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2495" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2495" s="4">
+        <v>9779</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C8AE80-0C0D-4343-BF98-64F518D55BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B104CD59-80B0-4DA2-9F07-4D41607A647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5937" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5988" uniqueCount="1346">
   <si>
     <t>Name</t>
   </si>
@@ -4048,6 +4048,21 @@
   </si>
   <si>
     <t>SHITU</t>
+  </si>
+  <si>
+    <t>malkeet rinku</t>
+  </si>
+  <si>
+    <t>0248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aman </t>
+  </si>
+  <si>
+    <t>UCB0002347</t>
+  </si>
+  <si>
+    <t>2857</t>
   </si>
 </sst>
 </file>
@@ -29770,7 +29785,7 @@
     </row>
     <row r="2310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2310" t="s">
-        <v>1306</v>
+        <v>1068</v>
       </c>
       <c r="B2310" s="6" t="s">
         <v>52</v>
@@ -31798,6 +31813,270 @@
       </c>
       <c r="C2495" s="4">
         <v>9779</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2496" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2496" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2496">
+        <v>8435</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2497" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B2497" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2497" s="4">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2498" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2498" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2498" s="4" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2499" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2499" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2499" s="4" t="s">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2500" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B2500" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2500" s="4">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2501" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2501" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2501" s="4">
+        <v>7578</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2502" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2502" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C2502" s="4">
+        <v>5237</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2503" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2503" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C2503" s="4">
+        <v>3671</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2504" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2504" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2504" s="4">
+        <v>8435</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2505" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2505" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2505" s="4">
+        <v>5969</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2506" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2506" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2506" s="4">
+        <v>9310</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2507" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2507" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2507" s="4">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2508" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2508" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2508" s="4">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2509" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2509" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2509" s="4">
+        <v>4057</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2510" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2510" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2510" s="4">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2511" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2511" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2511" s="4">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2512" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2512" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2512" s="4">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2513" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2513" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2513" s="4">
+        <v>4164</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2514" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2514" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2514" s="4">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2515" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2515" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2515" s="4">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2516" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2516" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2516" s="4">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2517" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2517" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2517" s="4">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2518" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2518" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2518" s="4">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2519" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2519" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2519" s="4" t="s">
+        <v>1345</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B104CD59-80B0-4DA2-9F07-4D41607A647A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA063157-F14E-4ED9-864D-3AD8CC715C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5988" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="1362">
   <si>
     <t>Name</t>
   </si>
@@ -4063,6 +4063,54 @@
   </si>
   <si>
     <t>2857</t>
+  </si>
+  <si>
+    <t>7811</t>
+  </si>
+  <si>
+    <t>0678</t>
+  </si>
+  <si>
+    <t>0112</t>
+  </si>
+  <si>
+    <t>HARMEET GAWADI</t>
+  </si>
+  <si>
+    <t>UTIB0005387</t>
+  </si>
+  <si>
+    <t>GSCBOKTC013</t>
+  </si>
+  <si>
+    <t>BKID0003831</t>
+  </si>
+  <si>
+    <t>HDFC0CBMCBJ</t>
+  </si>
+  <si>
+    <t>CNRB0005316</t>
+  </si>
+  <si>
+    <t>0417</t>
+  </si>
+  <si>
+    <t>ICIC00USNDC</t>
+  </si>
+  <si>
+    <t>0040</t>
+  </si>
+  <si>
+    <t>0630</t>
+  </si>
+  <si>
+    <t>UBIN0918202</t>
+  </si>
+  <si>
+    <t>0331</t>
+  </si>
+  <si>
+    <t>IDIB000F518</t>
   </si>
 </sst>
 </file>
@@ -32079,6 +32127,710 @@
         <v>1345</v>
       </c>
     </row>
+    <row r="2520" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2520" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2520" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2520" s="4" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2521" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2521" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2521" s="4">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2522" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2522" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2522" s="4">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2523" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2523" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2523" s="4">
+        <v>9818</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2524" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2524" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2524" s="4">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2525" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2525" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2525" s="4">
+        <v>8880</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2526" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2526" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2526" s="4">
+        <v>6815</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2527" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2527" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2527" s="4">
+        <v>3905</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2528" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2528" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2528" s="4" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2529" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2529" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2529" s="4">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2530" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2530" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2530" s="4" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2531" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2531" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2531" s="4">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2532" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2532" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2532" s="4">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2533" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2533" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2533" s="4">
+        <v>6541</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2534" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2534" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2534" s="4">
+        <v>8384</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2535" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2535" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2535" s="4">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2536" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2536" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2536" s="4">
+        <v>8379</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2537" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2537" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2537" s="4" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2538" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2538" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2538" s="4">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2539" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2539" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2539" s="4">
+        <v>8175</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2540" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2540" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2540" s="4">
+        <v>3584</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2541" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2541" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2541" s="4">
+        <v>3788</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2542" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2542" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2542" s="4">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2543" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2543" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2543" s="4">
+        <v>9650</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2544" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2544" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2544" s="4">
+        <v>5632</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2545" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2545" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2545" s="4">
+        <v>3534</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2546" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2546" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2546" s="4">
+        <v>6868</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2547" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2547" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2547" s="4">
+        <v>4885</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2548" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B2548" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2548" s="4">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2549" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B2549" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2549" s="4">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2550" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B2550" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2550" s="4">
+        <v>5751</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2551" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2551" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2551" s="4">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2552" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B2552" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2552" s="4">
+        <v>5812</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2553" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2553" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2553" s="4">
+        <v>3885</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2554" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2554" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2554" s="4" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2555" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2555" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2555" s="4">
+        <v>8384</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2556" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2556" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2556" s="4">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2557" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2557" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2557" s="4">
+        <v>7486</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2558" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2558" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2558" s="4">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2559" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2559" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2559" s="4">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2560" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2560" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2560" s="4">
+        <v>6541</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2561" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2561" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2561" s="4">
+        <v>3581</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2562" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2562" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2562" s="4">
+        <v>8379</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2563" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2563" t="s">
+        <v>1350</v>
+      </c>
+      <c r="C2563" s="4">
+        <v>3182</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2564" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2564" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C2564" s="4">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2565" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2565" t="s">
+        <v>1352</v>
+      </c>
+      <c r="C2565" s="4" t="s">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2566" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B2566" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C2566" s="4">
+        <v>8679</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2567" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2567" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C2567" s="4" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2568" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2568" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2568" s="4">
+        <v>5471</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2569" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2569" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2569" s="4">
+        <v>5470</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2570" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2570" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C2570" s="4" t="s">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2571" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2571" t="s">
+        <v>1356</v>
+      </c>
+      <c r="C2571" s="4" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2572" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2572" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2572" s="4" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2573" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2573" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C2573" s="4" t="s">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2574" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2574" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2574">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2575" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2575" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2575">
+        <v>8907</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2576" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2576" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2576">
+        <v>8882</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2577" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2577" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2577">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2578" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2578" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2578">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2579" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2579" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2579">
+        <v>6198</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2580" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2580" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2580">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2581" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2581" t="s">
+        <v>647</v>
+      </c>
+      <c r="C2581">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2582" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2582" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C2582">
+        <v>8085</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2583" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2583" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C2583">
+        <v>1425</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">

--- a/src/assets/accounts.xlsx
+++ b/src/assets/accounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA063157-F14E-4ED9-864D-3AD8CC715C80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89E621B-37F7-4DA0-98E9-AE79598367D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6127" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6140" uniqueCount="1367">
   <si>
     <t>Name</t>
   </si>
@@ -4111,13 +4111,28 @@
   </si>
   <si>
     <t>IDIB000F518</t>
+  </si>
+  <si>
+    <t>FDRL0007777</t>
+  </si>
+  <si>
+    <t>GUMRELLLLLL</t>
+  </si>
+  <si>
+    <t>HARJIDER GAWADI</t>
+  </si>
+  <si>
+    <t>KIRAN DELHI</t>
+  </si>
+  <si>
+    <t>MEENU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4177,6 +4192,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4198,7 +4220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4214,6 +4236,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32831,6 +32854,72 @@
         <v>1425</v>
       </c>
     </row>
+    <row r="2584" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2584" s="6" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B2584" s="13" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C2584">
+        <v>8551</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2585" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B2585" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2585">
+        <v>8854</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2586" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B2586" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2586">
+        <v>7946</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2587" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B2587" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2587">
+        <v>7419</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2588" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B2588" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2588" s="4" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2589" s="6" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B2589" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2589">
+        <v>3320</v>
+      </c>
+    </row>
     <row r="1048572" spans="1:2" ht="12.75" x14ac:dyDescent="0.2"/>
     <row r="1048576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1048576" t="s">
